--- a/target/test-classes/TestData/TestData.xlsx
+++ b/target/test-classes/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20361"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6A3EF2-82B8-41C9-9DF9-4C75059293A0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5F0F1F-251C-45BD-9833-010732E8E178}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOwn Test Data" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,8 @@
     <sheet name="ReadingPoint Test Data" sheetId="6" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
     <sheet name="AddAchievement Test Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Create Activity Error Msg Data" sheetId="3" r:id="rId6"/>
+    <sheet name="Login By Parent Smoke Test Data" sheetId="7" r:id="rId6"/>
+    <sheet name="Create Activity Error Msg Data" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
   <si>
     <t>Cycling</t>
   </si>
@@ -208,6 +209,18 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>expectedScreen</t>
+  </si>
+  <si>
+    <t>expectedUser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satish Kshirsagar </t>
+  </si>
+  <si>
+    <t>Home,My Activities,My Stories,Virtue Week,Achievements,Enter Reading Minutes,Create Own,Ultimate Rewards,My Approval,Book List,Child Assessment,Calendar</t>
   </si>
 </sst>
 </file>
@@ -968,6 +981,49 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9006BE57-2217-433F-B62B-25202513D0AE}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="135.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE76969-77BE-4CF5-B26D-565FB05E9A5F}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/target/test-classes/TestData/TestData.xlsx
+++ b/target/test-classes/TestData/TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20361"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5F0F1F-251C-45BD-9833-010732E8E178}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A8F745-BEEE-40EB-8B3F-73D74E14FA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateOwn Test Data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="67">
   <si>
     <t>Cycling</t>
   </si>
@@ -217,10 +217,16 @@
     <t>expectedUser</t>
   </si>
   <si>
-    <t xml:space="preserve">Satish Kshirsagar </t>
-  </si>
-  <si>
-    <t>Home,My Activities,My Stories,Virtue Week,Achievements,Enter Reading Minutes,Create Own,Ultimate Rewards,My Approval,Book List,Child Assessment,Calendar</t>
+    <t>Rohit Salunkhe</t>
+  </si>
+  <si>
+    <t>Home,My Activities,My Stories,Parenting Virtue,Achievements,Enter Reading Minutes,Create Tasks,Ultimate Rewards,My Approval,Book List,Child Assessment,Calendar,Discovery Lab,Knowledge Center</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>9784587997</t>
   </si>
 </sst>
 </file>
@@ -282,8 +288,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -566,22 +572,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
+    <col min="12" max="12" width="25.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -628,7 +634,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -675,7 +681,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -730,13 +736,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB8A0DD-6115-4D03-8A59-5042935E0ADC}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="9" max="9" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="59.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -764,9 +770,8 @@
       <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -779,7 +784,7 @@
       <c r="D2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -807,9 +812,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32295D7-07FC-46B9-A96D-4809084E790C}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -838,7 +843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -851,7 +856,7 @@
       <c r="D2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -878,9 +883,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A25A53-32F2-4315-9A12-DA52E7A6ED94}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -908,18 +913,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C60738-FDC7-49E4-8AB9-64CD81403A94}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="8" max="8" width="31.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -945,7 +950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -983,13 +988,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9006BE57-2217-433F-B62B-25202513D0AE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="135.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="135.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,12 +1009,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>63</v>
@@ -1026,15 +1032,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE76969-77BE-4CF5-B26D-565FB05E9A5F}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1054,7 +1060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1094,7 +1100,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B4" s="2"/>
     </row>
   </sheetData>
